--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,7 +659,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-problems</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -851,7 +851,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -978,7 +978,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-clinicalimpression|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -1420,7 +1420,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="182.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
